--- a/TDD_examples/CASE_3_HTS_HVDC/conductor_definition.xlsx
+++ b/TDD_examples/CASE_3_HTS_HVDC/conductor_definition.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDUCTOR_files" sheetId="6" r:id="R09de45e143aa4601"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDUCTOR_input" sheetId="10" r:id="R2e298b70baab4bfe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDUCTOR_operation" sheetId="11" r:id="Ra74d97d975e54514"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDUCTOR_coupling" sheetId="8" r:id="R307c2e0b55cd472c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDUCTOR_files" sheetId="6" r:id="R8392ffdbba5d4de8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDUCTOR_input" sheetId="10" r:id="R229c75c6b7414feb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDUCTOR_operation" sheetId="11" r:id="R597833c6ce4b49a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDUCTOR_coupling" sheetId="8" r:id="Rb7e4478e30f84271"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,9 +53,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">EXTERNAL_GRID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">custom file name, extension can be xlsx, dat, csv or tsv. Possibility to define a single file with the spatial discretizations for all the conducrors or a file for each conductor (in the last case use different names for the files). No need to have the same extension!</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">EXTERNAL_CONTACT_PERIMETER</x:t>
@@ -793,8 +790,8 @@
       <x:c r="C15" s="47" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D15" s="52" t="s">
-        <x:v>14</x:v>
+      <x:c r="D15" s="52" t="str">
+        <x:v>Custom file name; the extension can be xlsx, dat, csv, or tsv. A single file may define the spatial discretization for all conductors, or a separate file may be used for each conductor (use different file names in the latter case). The files do not need to use the same extension.</x:v>
       </x:c>
       <x:c r="E15" s="47" t="str">
         <x:v>none</x:v>
@@ -802,7 +799,7 @@
     </x:row>
     <x:row r="16" ht="14.5" hidden="0" customHeight="1">
       <x:c r="A16" s="46" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B16" s="46" t="s">
         <x:v>1</x:v>
@@ -811,7 +808,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D16" s="52" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E16" s="47" t="str">
         <x:v>none</x:v>
@@ -903,7 +900,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D5" s="49" t="str">
-        <x:v>Diameter of the conductor if cylidrical geometry</x:v>
+        <x:v>Diameter of the conductor for cylindrical geometry.</x:v>
       </x:c>
       <x:c r="E5" s="48" t="n">
         <x:v>0.186</x:v>
@@ -971,7 +968,7 @@
         <x:v>integer</x:v>
       </x:c>
       <x:c r="D9" s="49" t="str">
-        <x:v>current flag: none = current is not defined, bypass the electric module; 0 = constant; -1 = read from file; -2 = external function for current and its derivative after taudum; </x:v>
+        <x:v>Current definition mode: None = current is not defined and the electric module is bypassed; 0 = constant; -1 = read from file; -2 = user-defined external function for current and its derivative.</x:v>
       </x:c>
       <x:c r="E9" s="61" t="str">
         <x:v>none</x:v>
@@ -1005,7 +1002,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D11" s="49" t="str">
-        <x:v>flag to define the solution method: BE = Backward Euler; CN = Crank Nicholson; AM4 = Adams Moulton order 4</x:v>
+        <x:v>Flag used to define the solution method: BE = Backward Euler; CN = Crank-Nicolson; AM4 = fourth-order Adams-Moulton.</x:v>
       </x:c>
       <x:c r="E11" s="47" t="str">
         <x:v>BE</x:v>
@@ -1056,7 +1053,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D14" s="49" t="str">
-        <x:v>fraction of the outer lateral surface of the conductor that is subjetced to radiative heat exchange. Sould be in range [0,1].</x:v>
+        <x:v>Fraction of the outer lateral surface of the conductor subjected to radiative heat exchange. Must be in the range [0, 1].</x:v>
       </x:c>
       <x:c r="E14" s="47" t="n">
         <x:v>1</x:v>
@@ -1073,7 +1070,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D15" s="49" t="str">
-        <x:v>fraction of the outer lateral surface of the conductor that is subjetced to convective heat exchange. Sould be in range [0,1].</x:v>
+        <x:v>Fraction of the outer lateral surface of the conductor subjected to convective heat exchange. Must be in the range [0, 1].</x:v>
       </x:c>
       <x:c r="E15" s="47" t="n">
         <x:v>1</x:v>
@@ -1090,7 +1087,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D16" s="49" t="str">
-        <x:v>flag to define the electric solution method: BE = Backward Euler; CN = Crank Nicholson</x:v>
+        <x:v>Flag used to define the electric solution method: BE = Backward Euler; CN = Crank-Nicolson.</x:v>
       </x:c>
       <x:c r="E16" s="47" t="str">
         <x:v>BE</x:v>
@@ -1325,7 +1322,7 @@
         <x:v>integer</x:v>
       </x:c>
       <x:c r="D10" s="64" t="str">
-        <x:v>flag to select the method to evaluate the self inductance. Possible values: 0 = constant value from variable SEL_INDUCTANCE; 1 = mode 1; 2 = mode 2. Defaults to 1</x:v>
+        <x:v>Flag used to select the method for evaluating the self-inductance. Possible values: 0 = constant value from variable SELF_INDUCTANCE; 1 = mode 1; 2 = mode 2. Defaults to 1.</x:v>
       </x:c>
       <x:c r="E10" s="47" t="n">
         <x:v>2</x:v>
@@ -1359,7 +1356,7 @@
         <x:v>integer</x:v>
       </x:c>
       <x:c r="D12" s="64" t="str">
-        <x:v>Flag to select the solver for the electric module. Possible values: 0= steady state; 1 = transient. Defaults to 1. N.B. At the time being the steady solution is not availabye, althoug it works, to be consistent with the thermal hydrauilc solution.</x:v>
+        <x:v>Flag used to select the electric solver. Possible values: 0 = steady-state; 1 = transient. Defaults to 1.</x:v>
       </x:c>
       <x:c r="E12" s="47" t="n">
         <x:v>1</x:v>
